--- a/leads/Gulf_Clients.xlsx
+++ b/leads/Gulf_Clients.xlsx
@@ -599,65 +599,572 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>AG Metal Industry LLC</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>info@agmetal.ae</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>+971 52 129 4509</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>https://agmetal.ae/</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Al Jurf Industrial Area 2, Ajman, UAE</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Custom steel fabricator running a GoDaddy Website Builder page — looks like a placeholder vs ISO project work.</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Fabrication brand site replacing GoDaddy builder</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>sales@agmetal.ae and wa.me/971521294509 published.</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AG Metal Industry LLC: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Al Jurf Industrial Area 2, Ajman, UAE, I came across AG Metal Industry LLC.
+I reviewed AG Metal Industry LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with fabrication brand site replacing godaddy builder. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across AG Metal Industry LLC while reviewing industrial suppliers in Al Jurf Industrial Area 2 — custom steel fabricator running a GoDaddy Website Builder page — looks like a placeholder vs ISO project work..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with fabrication brand site replacing godaddy builder. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>https://agmetal.ae/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="72" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Al Ramlah Garage</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>+971 52 896 9596</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://alramlahgarage.com/contact/</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Al Qusais, Dubai / Al Khuzam, Ras Al Khaimah, UAE</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Multi-branch garage site shows 0 happy customers / 0 experts — looks unfinished for Dubai and RAK service bookings.</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Garage website + WhatsApp booking</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>No public email; WhatsApp/mobile published.</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Al Ramlah Garage: test-drive leads are leaking online</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing automotive businesses in Al Qusais, Dubai / Al Khuzam, Ras Al Khaimah, UAE, I came across Al Ramlah Garage.
+I reviewed Al Ramlah Garage's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, test-drive and service bookings now start online — weak dealer sites lose leads to competitors.
+At DMC Creatives Studio we help Gulf businesses with garage website + whatsapp booking. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I checked Al Ramlah Garage's site — multi-branch garage site shows 0 happy customers / 0 experts — looks unfinished for Dubai and RAK service bookings..
+Most garage bookings in Dubai/RAK now start on Google or WhatsApp. A mobile site with service list + click-to-call helps you capture walk-ins.
+We help with garage website + whatsapp booking. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>https://alramlahgarage.com/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sahara Medical Centre</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>info@saharamedicalcentre.ae</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>+971 50 882 1590</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://saharamedicalcentre.ae/</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Al Nahda, Sharjah, UAE</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Clinic says it was newly revamped; site still reads as a generic Sharjah dental landing page rather than a conversion-ready brand.</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>New-clinic website + booking funnel</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Public WhatsApp and email on site.</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Sahara Medical Centre: patients shortlist clinics online first</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing healthcare businesses in Al Nahda, Sharjah, UAE, I came across Sahara Medical Centre.
+Sahara Medical Centre looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
+In this category, patients compare clinics online before they call — a clear website and booking path wins the enquiry.
+At DMC Creatives Studio we help Gulf businesses with new-clinic website + booking funnel. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I saw Sahara Medical Centre launching in Al Nahda — strong brand, but most enquiries still land on WhatsApp/Instagram instead of a owned website.
+A simple 5-page site (About, Services, Gallery, Contact + WhatsApp button) helps you look established when buyers Google you.
+We help with new-clinic website + booking funnel. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>https://saharamedicalcentre.ae/index.php/dental-clinic-sharjah/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Emirates Industrial Filters Co.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>info@eif.ae</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>+971 50 984 4298</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.eif.ae/</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>New Industrial Area, Ajman, UAE</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Founded 2000 filtration manufacturer; site is a generic template with repeated CTAs, not a spec-sheet/RFQ catalogue.</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>B2B filtration catalogue + RFQ</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp published on homepage.</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Emirates Industrial Filters Co.: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in New Industrial Area, Ajman, UAE, I came across Emirates Industrial Filters Co..
+I reviewed Emirates Industrial Filters Co.'s current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with b2b filtration catalogue + rfq. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Emirates Industrial Filters Co. while reviewing industrial suppliers in New Industrial Area — founded 2000 filtration manufacturer; site is a generic template with repeated CTAs, not a spec-sheet/RFQ catalogue..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with b2b filtration catalogue + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.eif.ae/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Up To Date Medical Center</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>info@uptodate.ae</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>+971 50 680 5420</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://uptodate.ae/</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Al Dhiyafah, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Elementor default-logo clinic site; name promises current care but the digital presence looks unfinished.</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Clinic brand site + WhatsApp booking</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Public WhatsApp on site.</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Up To Date Medical Center: patients shortlist clinics online first</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing healthcare businesses in Al Dhiyafah, Dubai, UAE, I came across Up To Date Medical Center.
+I reviewed Up To Date Medical Center's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, patients compare clinics online before they call — a clear website and booking path wins the enquiry.
+At DMC Creatives Studio we help Gulf businesses with clinic brand site + whatsapp booking. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I was comparing clinics in Al Dhiyafah and noticed Up To Date Medical Center's website — elementor default-logo clinic site; name promises current care but the digital presence looks unfinished..
+Most patients shortlist 2–3 clinics on mobile before they call. A clean site with WhatsApp booking usually wins that first enquiry.
+We help with clinic brand site + whatsapp booking. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>https://uptodate.ae/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>Adam Medical Centre</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Dr. Saleel Valiyaveettil</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Specialist Physician</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>info@adammedicalcentre.com</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>+971 4 335 5011</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>https://adammedicalcentre.com/</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Clinic site is a leftover hospital template: Oman Badr Al Samaa copy, typos (Orthopediacs, PHYSIOTHERAPHY) and last news from 2021.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Clinic website rebuild + appointment CRM</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Named doctors on site; template content is clearly unfinished/outdated.</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Adam Medical Centre: patients shortlist clinics online first</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Hi Saleel,
 While reviewing healthcare businesses in Dubai, UAE, I came across Adam Medical Centre.
@@ -672,89 +1179,891 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Hi Saleel,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Dubai, UAE and noticed Adam Medical Centre's website looks outdated for today's market.
-We can help with clinic website rebuild + appointment crm. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
+I'm Vaibhav from DMC Creatives Studio (India). I was comparing clinics in Dubai and noticed Adam Medical Centre's website — clinic site is a leftover hospital template: Oman Badr Al Samaa copy, typos (Orthopediacs, PHYSIOTHERAPHY) and last….
+Most patients shortlist 2–3 clinics on mobile before they call. A clean site with WhatsApp booking usually wins that first enquiry.
+We help with clinic website rebuild + appointment crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>https://adammedicalcentre.com/</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="72" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="8" ht="72" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Green Gold Lubricants</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>info@greengoldoils.com</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>+971 56 484 7356</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>https://greengoldoils.com/</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Al Sajja, Sharjah, UAE</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>White-label lubricant maker with two WhatsApp numbers but a thin brand site vs OEM/catalogue buyers.</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Brand + private-label catalogue website</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Two mobiles published.</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Green Gold Lubricants: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Al Sajja, Sharjah, UAE, I came across Green Gold Lubricants.
+I reviewed Green Gold Lubricants's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with brand + private-label catalogue website. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Green Gold Lubricants while reviewing industrial suppliers in Al Sajja — white-label lubricant maker with two WhatsApp numbers but a thin brand site vs OEM/catalogue buyers..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with brand + private-label catalogue website. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>https://greengoldoils.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Al Mahboob Lubricants &amp; Oil Industries LLC</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>info@almahboobgroup.com</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>+971 50 746 8471</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>https://almahboobgroup.com/</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Industrial Area 11, Sharjah, UAE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2002 lubricant manufacturer still on a basic slider brochure site; B2B buyers expect a product catalogue and RFQ path.</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturer catalogue site + RFQ WhatsApp CRM</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp published on homepage.</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Al Mahboob Lubricants &amp; Oil Industries LLC: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Industrial Area 11, Sharjah, UAE, I came across Al Mahboob Lubricants &amp; Oil Industries LLC.
+I reviewed Al Mahboob Lubricants &amp; Oil Industries LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with manufacturer catalogue site + rfq whatsapp crm. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Al Mahboob Lubricants &amp; Oil Industries LLC while reviewing industrial suppliers in Industrial Area 11 — 2002 lubricant manufacturer still on a basic slider brochure site; B2B buyers expect a product catalogue and RFQ path..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with manufacturer catalogue site + rfq whatsapp crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>https://almahboobgroup.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="72" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Al Najam Transport</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>alnajamllc@gmail.com</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>+971 52 953 3220</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://alnajamtransport.com/school-transport-service-ras-al-khaimah-ajman/</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah / Ajman, UAE</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>School-bus operator using Gmail and a thin service page instead of a parent-trust brand site for RAK/Ajman contracts.</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Transport company website + school-contract enquiry</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Second mobile +971 54 787 5553 and alsaifeellc@gmail.com also listed.</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Al Najam Transport's website still looks stuck in the past</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing services businesses in Ras Al Khaimah / Ajman, UAE, I came across Al Najam Transport.
+I reviewed Al Najam Transport's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, serious clients still Google you — a weak site quietly costs you deals.
+At DMC Creatives Studio we help Gulf businesses with transport company website + school-contract enquiry. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I reviewed Al Najam Transport in Ras Al Khaimah / Ajman — school-bus operator using Gmail and a thin service page instead of a parent-trust brand site for RAK/Ajman contracts..
+Local service buyers trust a proper website over Gmail/listing pages when they compare vendors.
+We help with transport company website + school-contract enquiry. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>https://alnajamtransport.com/school-transport-service-ras-al-khaimah-ajman/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="72" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>NaasBay (HERBZE)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Hotel / F&amp;B</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>+971 58 103 9328</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/naasbay</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2025 UAE F&amp;B startup launching HERBZE via LinkedIn/WhatsApp — no owned conversion website for distributors or consumers.</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Launch website + distributor landing page</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Second WhatsApp +971 54 494 1393 listed on LinkedIn posts.</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>NaasBay: buyers search Google before they call</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing hotel / f&amp;b businesses in Dubai, UAE, I came across NaasBay (HERBZE).
+NaasBay (HERBZE) looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
+In this category, guests and corporates book the hotel that looks trustworthy and easy on mobile.
+At DMC Creatives Studio we help Gulf businesses with launch website + distributor landing page. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I saw NaasBay (HERBZE) launching in Dubai — strong brand, but most enquiries still land on WhatsApp/Instagram instead of a owned website.
+A simple 5-page site (About, Services, Gallery, Contact + WhatsApp button) helps you look established when buyers Google you.
+We help with launch website + distributor landing page. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/naasbay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Green Gold Trading Company (Dubai)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Trading</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>dubai@green-gold.co</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>+971 4 252 8284</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Al Ras, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Dubai Al Ras branch is listed with email and phone but a blank Website field — no owned UAE site for the trading desk.</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>UAE branch website + enquiry CRM</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Contact published on group contact page.</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Green Gold Trading Company: buyers search Google before they call</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing trading businesses in Al Ras, Dubai, UAE, I came across Green Gold Trading Company (Dubai).
+Green Gold Trading Company (Dubai) looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
+In this category, importers and distributors lose RFQs when the catalogue site looks older than the stock.
+At DMC Creatives Studio we help Gulf businesses with uae branch website + enquiry crm. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I saw Green Gold Trading Company (Dubai) launching in Al Ras — strong brand, but most enquiries still land on WhatsApp/Instagram instead of a owned website.
+A simple 5-page site (About, Services, Gallery, Contact + WhatsApp button) helps you look established when buyers Google you.
+We help with uae branch website + enquiry crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>https://green-gold.co/en/contact-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>SJS Enersol Engineering Works LLC</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Trading</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>info@sjsenersol.ae</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>+971 56 761 6172</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>https://sjsenersol.com/contact/</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>New Industrial Area, Umm Al Quwain, UAE</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>UAQ fasteners/pipes house with mixed domains (sjsenersol.ae vs sjsengg.ae) and a stockist site that does not match a manufacturing brand.</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>One brand site + catalogue for fasteners and fabrication</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Fabrication WhatsApp +971 58 8918432 also listed.</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>SJS Enersol Engineering Works LLC's website still looks stuck in the past</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing trading businesses in New Industrial Area, Umm Al Quwain, UAE, I came across SJS Enersol Engineering Works LLC.
+I reviewed SJS Enersol Engineering Works LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, importers and distributors lose RFQs when the catalogue site looks older than the stock.
+At DMC Creatives Studio we help Gulf businesses with one brand site + catalogue for fasteners and fabrication. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across SJS Enersol Engineering Works LLC while reviewing industrial suppliers in New Industrial Area — uAQ fasteners/pipes house with mixed domains (sjsenersol.ae vs sjsengg.ae) and a stockist site that does not match a….
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with one brand site + catalogue for fasteners and fabrication. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>https://sjsenersol.com/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="72" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>AL RIYADA Metal Industrial LLC</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>info@alriyadametals.com</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>+971 6 538 7221</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>https://alriyadametals.com/</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Emirates Industrial City, Al Sajja, Sharjah, UAE</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Thin metal-fabrication brochure; awkward English and no project/RFQ catalogue for UAE contractors.</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Fabrication catalogue + RFQ CRM</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Public email and landline on homepage.</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>AL RIYADA Metal Industrial LLC: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Emirates Industrial City, Al Sajja, Sharjah, UAE, I came across AL RIYADA Metal Industrial LLC.
+I reviewed AL RIYADA Metal Industrial LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with fabrication catalogue + rfq crm. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across AL RIYADA Metal Industrial LLC while reviewing industrial suppliers in Emirates Industrial City — thin metal-fabrication brochure; awkward English and no project/RFQ catalogue for UAE contractors..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with fabrication catalogue + rfq crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>https://alriyadametals.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="72" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>AL Muraqib Fiber Glass Industry L.L.C</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>info@almuraqib.ae</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>+971 6 569 1110</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>https://almuraqib.ae/contact-us/</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Al Bataeh Industrial Area, Sharjah, UAE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Copyright 2016–2022 industrial site with a broken Google Map embed — looks abandoned vs GRP tank buyers' expectations.</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Industrial product site + quotation form</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>sales@almuraqib.ae also published.</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>AL Muraqib Fiber Glass Industry L.L.C: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Al Bataeh Industrial Area, Sharjah, UAE, I came across AL Muraqib Fiber Glass Industry L.L.C.
+I reviewed AL Muraqib Fiber Glass Industry L.L.C's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with industrial product site + quotation form. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across AL Muraqib Fiber Glass Industry L.L.C while reviewing industrial suppliers in Al Bataeh Industrial Area — copyright 2016–2022 industrial site with a broken Google Map embed — looks abandoned vs GRP tank buyers' expectations..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with industrial product site + quotation form. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>https://almuraqib.ae/contact-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Advanced Medical Center (AMC Muscat)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>info@amcmuscat.com</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>+968 9257 0007</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>https://amc-muscat.com/</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Qurum, Muscat, Oman</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Qurum polyclinic still on an old form/FAQ site; WhatsApp booking number exists but the digital experience is dated.</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>Clinic website + WhatsApp appointments</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Landline 22826306 also published.</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>Advanced Medical Center: patients shortlist clinics online first</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing healthcare businesses in Qurum, Muscat, Oman, I came across Advanced Medical Center (AMC Muscat).
@@ -769,683 +2078,95 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Qurum, Muscat, Oman and noticed Advanced Medical Center (AMC Muscat)'s website looks outdated for today's market.
-We can help with clinic website + whatsapp appointments. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I was comparing clinics in Qurum and noticed Advanced Medical Center (AMC Muscat)'s website — qurum polyclinic still on an old form/FAQ site; WhatsApp booking number exists but the digital experience is dated..
+Most patients shortlist 2–3 clinics on mobile before they call. A clean site with WhatsApp booking usually wins that first enquiry.
+We help with clinic website + whatsapp appointments. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>https://amc-muscat.com/contactus/</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>AG Metal Industry LLC</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Al-Noor Plastic Factory</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>info@agmetal.ae</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>+971 52 129 4509</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>https://agmetal.ae/</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Al Jurf Industrial Area 2, Ajman, UAE</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Custom steel fabricator running a GoDaddy Website Builder page — looks like a placeholder vs ISO project work.</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Fabrication brand site replacing GoDaddy builder</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>sales@agmetal.ae and wa.me/971521294509 published.</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>AG Metal Industry LLC: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Al Jurf Industrial Area 2, Ajman, UAE, I came across AG Metal Industry LLC.
-I reviewed AG Metal Industry LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with fabrication brand site replacing godaddy builder. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Jurf Industrial Area 2, Ajman, UAE and noticed AG Metal Industry LLC's website looks outdated for today's market.
-We can help with fabrication brand site replacing godaddy builder. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>https://agmetal.ae/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Al Mahboob Lubricants &amp; Oil Industries LLC</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>info@almahboobgroup.com</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>+971 50 746 8471</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>https://almahboobgroup.com/</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Industrial Area 11, Sharjah, UAE</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>2002 lubricant manufacturer still on a basic slider brochure site; B2B buyers expect a product catalogue and RFQ path.</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturer catalogue site + RFQ WhatsApp CRM</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>WhatsApp published on homepage.</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Al Mahboob Lubricants &amp; Oil Industries LLC: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Industrial Area 11, Sharjah, UAE, I came across Al Mahboob Lubricants &amp; Oil Industries LLC.
-I reviewed Al Mahboob Lubricants &amp; Oil Industries LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with manufacturer catalogue site + rfq whatsapp crm. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Industrial Area 11, Sharjah, UAE and noticed Al Mahboob Lubricants &amp; Oil Industries LLC's website looks outdated for today's market.
-We can help with manufacturer catalogue site + rfq whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>https://almahboobgroup.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>AL Muraqib Fiber Glass Industry L.L.C</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>info@almuraqib.ae</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>+971 6 569 1110</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>https://almuraqib.ae/contact-us/</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Al Bataeh Industrial Area, Sharjah, UAE</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Copyright 2016–2022 industrial site with a broken Google Map embed — looks abandoned vs GRP tank buyers' expectations.</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Industrial product site + quotation form</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>sales@almuraqib.ae also published.</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>AL Muraqib Fiber Glass Industry L.L.C: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Al Bataeh Industrial Area, Sharjah, UAE, I came across AL Muraqib Fiber Glass Industry L.L.C.
-I reviewed AL Muraqib Fiber Glass Industry L.L.C's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with industrial product site + quotation form. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Bataeh Industrial Area, Sharjah, UAE and noticed AL Muraqib Fiber Glass Industry L.L.C's website looks outdated for today's market.
-We can help with industrial product site + quotation form. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t>https://almuraqib.ae/contact-us/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Al Najam Transport</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>alnajamllc@gmail.com</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>+971 52 953 3220</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>https://alnajamtransport.com/school-transport-service-ras-al-khaimah-ajman/</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah / Ajman, UAE</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>School-bus operator using Gmail and a thin service page instead of a parent-trust brand site for RAK/Ajman contracts.</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Transport company website + school-contract enquiry</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Second mobile +971 54 787 5553 and alsaifeellc@gmail.com also listed.</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Al Najam Transport's website still looks stuck in the past</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing services businesses in Ras Al Khaimah / Ajman, UAE, I came across Al Najam Transport.
-I reviewed Al Najam Transport's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, serious clients still Google you — a weak site quietly costs you deals.
-At DMC Creatives Studio we help Gulf businesses with transport company website + school-contract enquiry. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Ras Al Khaimah / Ajman, UAE and noticed Al Najam Transport's website looks outdated for today's market.
-We can help with transport company website + school-contract enquiry. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>https://alnajamtransport.com/school-transport-service-ras-al-khaimah-ajman/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Al Ramlah Garage</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Automotive</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>+971 52 896 9596</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>https://alramlahgarage.com/contact/</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Al Qusais, Dubai / Al Khuzam, Ras Al Khaimah, UAE</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Multi-branch garage site shows 0 happy customers / 0 experts — looks unfinished for Dubai and RAK service bookings.</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Garage website + WhatsApp booking</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>No public email; WhatsApp/mobile published.</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>Al Ramlah Garage: test-drive leads are leaking online</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing automotive businesses in Al Qusais, Dubai / Al Khuzam, Ras Al Khaimah, UAE, I came across Al Ramlah Garage.
-I reviewed Al Ramlah Garage's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, test-drive and service bookings now start online — weak dealer sites lose leads to competitors.
-At DMC Creatives Studio we help Gulf businesses with garage website + whatsapp booking. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Qusais, Dubai / Al Khuzam, Ras Al Khaimah, UAE and noticed Al Ramlah Garage's website looks outdated for today's market.
-We can help with garage website + whatsapp booking. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>https://alramlahgarage.com/contact/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>AL RIYADA Metal Industrial LLC</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>info@alriyadametals.com</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>+971 6 538 7221</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>https://alriyadametals.com/</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Emirates Industrial City, Al Sajja, Sharjah, UAE</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Thin metal-fabrication brochure; awkward English and no project/RFQ catalogue for UAE contractors.</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Fabrication catalogue + RFQ CRM</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Public email and landline on homepage.</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>AL RIYADA Metal Industrial LLC: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Emirates Industrial City, Al Sajja, Sharjah, UAE, I came across AL RIYADA Metal Industrial LLC.
-I reviewed AL RIYADA Metal Industrial LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with fabrication catalogue + rfq crm. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Emirates Industrial City, Al Sajja, Sharjah, UAE and noticed AL RIYADA Metal Industrial LLC's website looks outdated for today's market.
-We can help with fabrication catalogue + rfq crm. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>https://alriyadametals.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Al-Noor Plastic Factory</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>info@npf.qa</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>+974 3399 9380</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>https://npf.qa/contact/</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>New Industrial Area, Doha, Qatar</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Qatar industrial plastics plant; contact works but the brand site is a thin factory page vs GCC RFQ buyers.</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Factory catalogue + WhatsApp RFQ</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Sales mobiles and cm@npf.qa / finance@npf.qa published.</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>Al-Noor Plastic Factory: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in New Industrial Area, Doha, Qatar, I came across Al-Noor Plastic Factory.
@@ -1460,190 +2181,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in New Industrial Area, Doha, Qatar and noticed Al-Noor Plastic Factory's website looks outdated for today's market.
-We can help with factory catalogue + whatsapp rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Al-Noor Plastic Factory while reviewing industrial suppliers in New Industrial Area — qatar industrial plastics plant; contact works but the brand site is a thin factory page vs GCC RFQ buyers..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with factory catalogue + whatsapp rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q10" s="5" t="inlineStr">
+      <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>https://npf.qa/contact/</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="72" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="18" ht="72" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Emirates Industrial Filters Co.</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>epi AL-Ebda Plastic Industries</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>info@eif.ae</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>+971 50 984 4298</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.eif.ae/</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>New Industrial Area, Ajman, UAE</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Founded 2000 filtration manufacturer; site is a generic template with repeated CTAs, not a spec-sheet/RFQ catalogue.</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>B2B filtration catalogue + RFQ</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>WhatsApp published on homepage.</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Emirates Industrial Filters Co.: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in New Industrial Area, Ajman, UAE, I came across Emirates Industrial Filters Co..
-I reviewed Emirates Industrial Filters Co.'s current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with b2b filtration catalogue + rfq. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in New Industrial Area, Ajman, UAE and noticed Emirates Industrial Filters Co.'s website looks outdated for today's market.
-We can help with b2b filtration catalogue + rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.eif.ae/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>epi AL-Ebda Plastic Industries</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>info@epi-qatar.com</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>https://www.epi-qatar.com/contact</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>New Industrial Area, Doha, Qatar</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>New Industrial Area plastics company with emails on a near-empty contact page — needs a real factory site.</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>Plastics factory website + RFQ</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>sales@epi-qatar.com also listed in public search/contact copy.</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>epi AL-Ebda Plastic Industries: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in New Industrial Area, Doha, Qatar, I came across epi AL-Ebda Plastic Industries.
@@ -1658,190 +2280,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in New Industrial Area, Doha, Qatar and noticed epi AL-Ebda Plastic Industries's website looks outdated for today's market.
-We can help with plastics factory website + rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across epi AL-Ebda Plastic Industries while reviewing industrial suppliers in New Industrial Area — new Industrial Area plastics company with emails on a near-empty contact page — needs a real factory site..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with plastics factory website + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>https://www.epi-qatar.com/contact</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Green Gold Lubricants</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>info@greengoldoils.com</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>+971 56 484 7356</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>https://greengoldoils.com/</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Al Sajja, Sharjah, UAE</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>White-label lubricant maker with two WhatsApp numbers but a thin brand site vs OEM/catalogue buyers.</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>Brand + private-label catalogue website</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Two mobiles published.</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Green Gold Lubricants: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Al Sajja, Sharjah, UAE, I came across Green Gold Lubricants.
-I reviewed Green Gold Lubricants's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with brand + private-label catalogue website. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Sajja, Sharjah, UAE and noticed Green Gold Lubricants's website looks outdated for today's market.
-We can help with brand + private-label catalogue website. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>https://greengoldoils.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Green Gold Trading Co.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Trading</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>info@green-gold.co</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>920008925</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>https://green-gold.co/en/contact-us/</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Al Aziziyah, Riyadh, Saudi Arabia</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Multi-city KSA trader; contact page dumps every branch with mixed/wrong emails (Dammam listed as jeddah@) — the site does not match a national brand.</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>National brand website + branch locator</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>factory@green-gold.co and city emails published.</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>Green Gold Trading Co.'s website still looks stuck in the past</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing trading businesses in Al Aziziyah, Riyadh, Saudi Arabia, I came across Green Gold Trading Co..
@@ -1856,182 +2379,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Aziziyah, Riyadh, Saudi Arabia and noticed Green Gold Trading Co.'s website looks outdated for today's market.
-We can help with national brand website + branch locator. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Green Gold Trading Co. while reviewing industrial suppliers in Al Aziziyah — multi-city KSA trader; contact page dumps every branch with mixed/wrong emails (Dammam listed as jeddah@) — the site….
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with national brand website + branch locator. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>https://green-gold.co/en/contact-us/</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="20" ht="72" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Green Gold Trading Company (Dubai)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Trading</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>dubai@green-gold.co</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>+971 4 252 8284</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Al Ras, Dubai, UAE</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Dubai Al Ras branch is listed with email and phone but a blank Website field — no owned UAE site for the trading desk.</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>UAE branch website + enquiry CRM</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Contact published on group contact page.</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Green Gold Trading Company: buyers search Google before they call</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing trading businesses in Al Ras, Dubai, UAE, I came across Green Gold Trading Company (Dubai).
-Green Gold Trading Company (Dubai) looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
-In this category, importers and distributors lose RFQs when the catalogue site looks older than the stock.
-At DMC Creatives Studio we help Gulf businesses with uae branch website + enquiry crm. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing new businesses in Al Ras, Dubai, UAE and noticed Green Gold Trading Company (Dubai) still needs a conversion-ready website for the Gulf market.
-We can help with uae branch website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>https://green-gold.co/en/contact-us/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>K-PAK (Kuwait Pack)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>kpak@kuwaitpack.com</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>+965 2472 1124</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>http://www.saudipack.com.sa/contactus.html</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>South Sabhan, Kuwait</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>Kuwait packing plant only appears on a 2008 HTTP sister-company page — no owned conversion website.</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>Owned packaging website + RFQ</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>Contact listed on Saudi Pack contactus.html.</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>K-PAK: buyers search Google before they call</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in South Sabhan, Kuwait, I came across K-PAK (Kuwait Pack).
@@ -2046,89 +2478,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in South Sabhan, Kuwait and noticed K-PAK (Kuwait Pack)'s website looks outdated for today's market.
-We can help with owned packaging website + rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across K-PAK (Kuwait Pack) while reviewing industrial suppliers in South Sabhan — kuwait packing plant only appears on a 2008 HTTP sister-company page — no owned conversion website..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with owned packaging website + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr">
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>http://www.saudipack.com.sa/contactus.html</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="72" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="21" ht="72" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Kuwait Polymer Company</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>info@kwpolymer.com</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>+965 2294 4544</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>https://www.kwpolymer.com/contacts.html</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Amgarah Industrial Area, Kuwait</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>Copyright 2020 EPS manufacturer site; department emails exist but the web experience is an old form page.</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>EPS product catalogue + enquiry CRM</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>sales@kwpolymer.com and marketing@kwpolymer.com published.</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>Kuwait Polymer Company: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Amgarah Industrial Area, Kuwait, I came across Kuwait Polymer Company.
@@ -2143,89 +2577,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Amgarah Industrial Area, Kuwait and noticed Kuwait Polymer Company's website looks outdated for today's market.
-We can help with eps product catalogue + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Kuwait Polymer Company while reviewing industrial suppliers in Amgarah Industrial Area — copyright 2020 EPS manufacturer site; department emails exist but the web experience is an old form page..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with eps product catalogue + enquiry crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>https://www.kwpolymer.com/contacts.html</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="72" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="22" ht="72" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Manama Scientific Company</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Trading</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>info@manamasc.com.bh</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>+973 1774 9010</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>https://manamascientific.com/contact-us/</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Alqudaybiyah, Manama, Bahrain</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>Medical equipment supplier contact is a generic template; WhatsApp button exists but the brand site does not sell the catalogue.</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>Medical-supply catalogue website + WhatsApp enquiry</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>Hotline +973 1774 9060 also listed.</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>Manama Scientific Company's website still looks stuck in the past</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing trading businesses in Alqudaybiyah, Manama, Bahrain, I came across Manama Scientific Company.
@@ -2240,89 +2676,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Alqudaybiyah, Manama, Bahrain and noticed Manama Scientific Company's website looks outdated for today's market.
-We can help with medical-supply catalogue website + whatsapp enquiry. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Manama Scientific Company while reviewing industrial suppliers in Alqudaybiyah — medical equipment supplier contact is a generic template; WhatsApp button exists but the brand site does not sell the….
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with medical-supply catalogue website + whatsapp enquiry. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr">
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>https://manamascientific.com/contact-us/</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="72" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="23" ht="72" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>MASABIK (Axles, Foundries &amp; Spare Parts Factory)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>sales@masabik.com</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>+966 13 812 1267</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>https://www.masabik.com/index.php/contact-us/contact-us</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Dammam Second Industrial City, Saudi Arabia</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Joomla table layout for a Dammam foundry with Riyadh/Jeddah branches — RFQ buyers expect a modern catalogue.</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>Foundry catalogue website + RFQ</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>Branch numbers on contact page.</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>MASABIK: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Dammam Second Industrial City, Saudi Arabia, I came across MASABIK (Axles, Foundries &amp; Spare Parts Factory).
@@ -2337,85 +2775,87 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Dammam Second Industrial City, Saudi Arabia and noticed MASABIK (Axles, Foundries &amp; Spare Parts Factory)'s website looks outdated for today's market.
-We can help with foundry catalogue website + rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across MASABIK (Axles, Foundries &amp; Spare Parts Factory) while reviewing industrial suppliers in Dammam Second Industrial City — joomla table layout for a Dammam foundry with Riyadh/Jeddah branches — RFQ buyers expect a modern catalogue..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with foundry catalogue website + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr">
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>https://www.masabik.com/index.php/contact-us/contact-us</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="72" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="24" ht="72" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Mekyal Muscat LLC</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>+968 7904 9019</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>https://mekyalmuscat.com/</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>Barka Industrial Estate, Oman</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>Process-instrumentation manufacturer site has typos (Thermpcouples) and a 2023 template footer — not bid-ready for GCC projects.</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>Instrumentation catalogue website</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>GSM published on homepage; no public email on the page fetched.</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>Mekyal Muscat LLC: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Barka Industrial Estate, Oman, I came across Mekyal Muscat LLC.
@@ -2430,89 +2870,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Barka Industrial Estate, Oman and noticed Mekyal Muscat LLC's website looks outdated for today's market.
-We can help with instrumentation catalogue website. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr">
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Mekyal Muscat LLC while reviewing industrial suppliers in Barka Industrial Estate — process-instrumentation manufacturer site has typos (Thermpcouples) and a 2023 template footer — not bid-ready for GCC….
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with instrumentation catalogue website. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
-      <c r="R20" s="3" t="inlineStr">
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t>https://mekyalmuscat.com/</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="72" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="25" ht="72" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>MPT Saudi Arabia</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>info@mpt.sa</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>+966 50 556 0191</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>https://mpt.sa/en/</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Riyadh, Saudi Arabia</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>Software/marketing firm site is broken (spaced testimonials, placeholder project names) — looks untrusted for Saudi buyers.</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>Agency website rebuild + Arabic/English lead form</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>Mobile published on homepage.</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>MPT Saudi Arabia's website still looks stuck in the past</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing services businesses in Riyadh, Saudi Arabia, I came across MPT Saudi Arabia.
@@ -2527,93 +2969,95 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Riyadh, Saudi Arabia and noticed MPT Saudi Arabia's website looks outdated for today's market.
-We can help with agency website rebuild + arabic/english lead form. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I reviewed MPT Saudi Arabia in Riyadh — software/marketing firm site is broken (spaced testimonials, placeholder project names) — looks untrusted for Saudi….
+Local service buyers trust a proper website over Gmail/listing pages when they compare vendors.
+We help with agency website rebuild + arabic/english lead form. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
-      <c r="R21" s="3" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>https://mpt.sa/en/</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="72" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="26" ht="72" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Muscat Express Hotel</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Hotel / F&amp;B</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>info@muscatexpresshotel.com</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>+968 2255 3303</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>https://muscatexpresshotel.com/contact/</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>Al Ghubrah, Muscat, Oman</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>Al Ghubrah hotel contact is a bare form; independent property needs a conversion-ready booking site.</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>Hotel website + WhatsApp reservations</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>reservations@muscatexpresshotel.com published.</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>Muscat Express Hotel: your website vs today's direct bookings</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing hotel / f&amp;b businesses in Al Ghubrah, Muscat, Oman, I came across Muscat Express Hotel.
@@ -2628,89 +3072,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Ghubrah, Muscat, Oman and noticed Muscat Express Hotel's website looks outdated for today's market.
-We can help with hotel website + whatsapp reservations. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I was reviewing businesses in Al Ghubrah and noticed Muscat Express Hotel's website looks outdated for today's Gulf market.
+Buyers judge readiness from your website before they ever call.
+We help with hotel website + whatsapp reservations. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr">
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t>https://muscatexpresshotel.com/contact/</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="72" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Muscat Hills Hotel</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Hotel / F&amp;B</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>info@muscathillshotel.com</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>+968 9122 7323</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>https://muscathillshotel.com/contact-us/</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Ghala Heights, Bawsher, Muscat, Oman</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Independent Muscat hotel; contact works but the site is a generic booking brochure vs OTA-ready brand.</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>Hotel website + direct-booking engine</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>gm@muscathillshotel.com and sales@ also published.</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>Muscat Hills Hotel: your website vs today's direct bookings</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing hotel / f&amp;b businesses in Ghala Heights, Bawsher, Muscat, Oman, I came across Muscat Hills Hotel.
@@ -2725,93 +3171,95 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Ghala Heights, Bawsher, Muscat, Oman and noticed Muscat Hills Hotel's website looks outdated for today's market.
-We can help with hotel website + direct-booking engine. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I was reviewing businesses in Ghala Heights and noticed Muscat Hills Hotel's website looks outdated for today's Gulf market.
+Buyers judge readiness from your website before they ever call.
+We help with hotel website + direct-booking engine. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
-      <c r="R23" s="3" t="inlineStr">
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>https://muscathillshotel.com/contact-us/</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="72" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Muscat Steel Industries Co. LLC</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>info@muscatsteel.com</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>+968 2444 6938</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>https://muscatsteel.com/group-companies/muscat-steel-industries-co-llc/contact-details/</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>Rusayl, Muscat, Oman</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>Group steel company still on old HTML tables for contact — not a modern mill/trading site.</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>Steel group website + RFQ</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>Email and landline on contact-details page.</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>Muscat Steel Industries Co. LLC: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Rusayl, Muscat, Oman, I came across Muscat Steel Industries Co. LLC.
@@ -2826,182 +3274,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Rusayl, Muscat, Oman and noticed Muscat Steel Industries Co. LLC's website looks outdated for today's market.
-We can help with steel group website + rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Muscat Steel Industries Co. LLC while reviewing industrial suppliers in Rusayl — group steel company still on old HTML tables for contact — not a modern mill/trading site..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with steel group website + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr">
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t>https://muscatsteel.com/group-companies/muscat-steel-industries-co-llc/contact-details/</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="72" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>NaasBay (HERBZE)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Hotel / F&amp;B</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>+971 58 103 9328</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/naasbay</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Dubai, UAE</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>2025 UAE F&amp;B startup launching HERBZE via LinkedIn/WhatsApp — no owned conversion website for distributors or consumers.</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>Launch website + distributor landing page</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>Second WhatsApp +971 54 494 1393 listed on LinkedIn posts.</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>NaasBay: buyers search Google before they call</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing hotel / f&amp;b businesses in Dubai, UAE, I came across NaasBay (HERBZE).
-NaasBay (HERBZE) looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
-In this category, guests and corporates book the hotel that looks trustworthy and easy on mobile.
-At DMC Creatives Studio we help Gulf businesses with launch website + distributor landing page. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing new businesses in Dubai, UAE and noticed NaasBay (HERBZE) still needs a conversion-ready website for the Gulf market.
-We can help with launch website + distributor landing page. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/naasbay</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="72" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Qatar German Gasket Factory</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>sales@qger.com</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>+974 4411 4404</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>https://www.qger.com/contact/</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>New Industrial Area, Doha, Qatar</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Contact page still lists http://qger.com; industrial gasket maker needs a bilingual product/RFQ site.</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>Product catalogue website + RFQ</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>sales@qger.com on contact page.</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>Qatar German Gasket Factory is still on HTTP — that hurts trust</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in New Industrial Area, Doha, Qatar, I came across Qatar German Gasket Factory.
@@ -3016,89 +3373,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in New Industrial Area, Doha, Qatar and noticed Qatar German Gasket Factory's website looks outdated for today's market.
-We can help with product catalogue website + rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Qatar German Gasket Factory while reviewing industrial suppliers in New Industrial Area — contact page still lists http://qger.com; industrial gasket maker needs a bilingual product/RFQ site..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with product catalogue website + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q26" s="3" t="inlineStr"/>
-      <c r="R26" s="3" t="inlineStr">
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>https://www.qger.com/contact/</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="72" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Reef Yemen Company (Kuwait)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Trading</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>reefyemen.kwt@gmail.com</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>+965 2491 1837</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>https://green-gold.co/en/contact-us/</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>Shuwaikh, Kuwait</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>Kuwait Shuwaikh trading desk uses Gmail and a sister-company listing instead of a local brand website.</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>Kuwait brand website + WhatsApp catalogue</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>Public Gmail and landline on Green Gold international-branches list.</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>Reef Yemen Company's website still looks stuck in the past</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N30" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing trading businesses in Shuwaikh, Kuwait, I came across Reef Yemen Company (Kuwait).
@@ -3113,198 +3472,99 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Shuwaikh, Kuwait and noticed Reef Yemen Company (Kuwait)'s website looks outdated for today's market.
-We can help with kuwait brand website + whatsapp catalogue. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Reef Yemen Company (Kuwait) while reviewing industrial suppliers in Shuwaikh — kuwait Shuwaikh trading desk uses Gmail and a sister-company listing instead of a local brand website..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with kuwait brand website + whatsapp catalogue. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
         <is>
           <t>https://green-gold.co/en/contact-us/</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="72" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Sahara Medical Centre</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>info@saharamedicalcentre.ae</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>+971 50 882 1590</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>https://saharamedicalcentre.ae/</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>Al Nahda, Sharjah, UAE</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>Clinic says it was newly revamped; site still reads as a generic Sharjah dental landing page rather than a conversion-ready brand.</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>New-clinic website + booking funnel</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>Public WhatsApp and email on site.</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>Sahara Medical Centre: patients shortlist clinics online first</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing healthcare businesses in Al Nahda, Sharjah, UAE, I came across Sahara Medical Centre.
-Sahara Medical Centre looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
-In this category, patients compare clinics online before they call — a clear website and booking path wins the enquiry.
-At DMC Creatives Studio we help Gulf businesses with new-clinic website + booking funnel. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing new businesses in Al Nahda, Sharjah, UAE and noticed Sahara Medical Centre still needs a conversion-ready website for the Gulf market.
-We can help with new-clinic website + booking funnel. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q28" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>https://saharamedicalcentre.ae/index.php/dental-clinic-sharjah/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="72" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Saudi Hadaid Factory</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Fuad AlShafeey</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>info@saudihadaid.com</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>+966 13 8309279</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>https://www.saudihadaid.com/</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>2nd Industrial City, Dammam, Saudi Arabia</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Heavy-industry factory still on old static HTML with awkward English — not a bid-ready Gulf contractor site.</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>Industrial contractor website + project sheets</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>Deputy GM Eyad F. AlShafeey, eyad@saudihadaid.com also published.</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>Saudi Hadaid Factory: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>Hi Fuad,
 While reviewing manufacturing businesses in 2nd Industrial City, Dammam, Saudi Arabia, I came across Saudi Hadaid Factory.
@@ -3319,89 +3579,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O31" s="3" t="inlineStr">
         <is>
           <t>Hi Fuad,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in 2nd Industrial City, Dammam, Saudi Arabia and noticed Saudi Hadaid Factory's website looks outdated for today's market.
-We can help with industrial contractor website + project sheets. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr">
+I'm Vaibhav from DMC Creatives Studio (India). I came across Saudi Hadaid Factory while reviewing industrial suppliers in 2nd Industrial City — heavy-industry factory still on old static HTML with awkward English — not a bid-ready Gulf contractor site..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with industrial contractor website + project sheets. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr">
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>https://www.saudihadaid.com/contact.html</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="72" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Saudi Packing Materials Manufacturing Co. (S-PAK)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>spak@saudipack.com</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>+966 2 608 2088</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>http://www.saudipack.com.sa/contactus.html</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Jeddah Industrial City, Saudi Arabia</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>HTTP-only table site with copyright 2008 — packaging plants in Jeddah and Dammam still look stuck in the past.</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>HTTPS catalogue rebuild + distributor locator</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>Dammam plant also listed on same contact page.</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>Saudi Packing Materials Manufacturing Co. is still on HTTP — that hurts trust</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Jeddah Industrial City, Saudi Arabia, I came across Saudi Packing Materials Manufacturing Co. (S-PAK).
@@ -3416,190 +3678,91 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Jeddah Industrial City, Saudi Arabia and noticed Saudi Packing Materials Manufacturing Co. (S-PAK)'s website looks outdated for today's market.
-We can help with https catalogue rebuild + distributor locator. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Saudi Packing Materials Manufacturing Co. (S-PAK) while reviewing industrial suppliers in Jeddah Industrial City — hTTP-only table site with copyright 2008 — packaging plants in Jeddah and Dammam still look stuck in the past..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with https catalogue rebuild + distributor locator. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr">
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t>http://www.saudipack.com.sa/contactus.html</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="72" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>SJS Enersol Engineering Works LLC</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Trading</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>info@sjsenersol.ae</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>+971 56 761 6172</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>https://sjsenersol.com/contact/</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>New Industrial Area, Umm Al Quwain, UAE</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>UAQ fasteners/pipes house with mixed domains (sjsenersol.ae vs sjsengg.ae) and a stockist site that does not match a manufacturing brand.</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>One brand site + catalogue for fasteners and fabrication</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>Fabrication WhatsApp +971 58 8918432 also listed.</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>SJS Enersol Engineering Works LLC's website still looks stuck in the past</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing trading businesses in New Industrial Area, Umm Al Quwain, UAE, I came across SJS Enersol Engineering Works LLC.
-I reviewed SJS Enersol Engineering Works LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, importers and distributors lose RFQs when the catalogue site looks older than the stock.
-At DMC Creatives Studio we help Gulf businesses with one brand site + catalogue for fasteners and fabrication. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in New Industrial Area, Umm Al Quwain, UAE and noticed SJS Enersol Engineering Works LLC's website looks outdated for today's market.
-We can help with one brand site + catalogue for fasteners and fabrication. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>https://sjsenersol.com/contact/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="72" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Tenhal Information Technology Company</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>info@tenhal.sa</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>+966 55 477 7441</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>https://tenhal.sa/</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>King Faisal, Riyadh, Saudi Arabia</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>Established 2024 Vision 2030 IT firm with a thin one-page site — new company still needs a credible services/case-study website.</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>New-company website + lead capture</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>contact@tenhal.sa also published. Two KSA mobiles.</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>Tenhal Information Technology Company: a new Gulf brand still needs a real website</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing services businesses in King Faisal, Riyadh, Saudi Arabia, I came across Tenhal Information Technology Company.
@@ -3614,93 +3777,95 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing new businesses in King Faisal, Riyadh, Saudi Arabia and noticed Tenhal Information Technology Company still needs a conversion-ready website for the Gulf market.
-We can help with new-company website + lead capture. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I saw Tenhal Information Technology Company launching in King Faisal — strong brand, but most enquiries still land on WhatsApp/Instagram instead of a owned website.
+A simple 5-page site (About, Services, Gallery, Contact + WhatsApp button) helps you look established when buyers Google you.
+We help with new-company website + lead capture. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q32" s="5" t="inlineStr">
+      <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
-      <c r="R32" s="3" t="inlineStr">
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t>https://tenhal.sa/</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="72" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>U-PAK FZC</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>upak@upakfzc.com</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>+971 7 244 7950</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>http://www.saudipack.com.sa/contactus.html</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>RAK Free Trade Zone, Ras Al Khaimah, UAE</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>RAK packaging unit listed on a 2008-copyright HTTP sister site — no strong owned brand website for buyers.</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>Packaging brand site + RFQ</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>Contact published on Saudi Pack contact page.</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>U-PAK FZC is still on HTTP — that hurts trust</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in RAK Free Trade Zone, Ras Al Khaimah, UAE, I came across U-PAK FZC.
@@ -3715,128 +3880,29 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in RAK Free Trade Zone, Ras Al Khaimah, UAE and noticed U-PAK FZC's website looks outdated for today's market.
-We can help with packaging brand site + rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across U-PAK FZC while reviewing industrial suppliers in RAK Free Trade Zone — rAK packaging unit listed on a 2008-copyright HTTP sister site — no strong owned brand website for buyers..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with packaging brand site + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="3" t="inlineStr">
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
         <is>
           <t>http://www.saudipack.com.sa/contactus.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="72" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Up To Date Medical Center</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>info@uptodate.ae</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>+971 50 680 5420</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>https://uptodate.ae/</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>Al Dhiyafah, Dubai, UAE</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>Elementor default-logo clinic site; name promises current care but the digital presence looks unfinished.</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>Clinic brand site + WhatsApp booking</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>Public WhatsApp on site.</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>Up To Date Medical Center: patients shortlist clinics online first</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing healthcare businesses in Al Dhiyafah, Dubai, UAE, I came across Up To Date Medical Center.
-I reviewed Up To Date Medical Center's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, patients compare clinics online before they call — a clear website and booking path wins the enquiry.
-At DMC Creatives Studio we help Gulf businesses with clinic brand site + whatsapp booking. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Dhiyafah, Dubai, UAE and noticed Up To Date Medical Center's website looks outdated for today's market.
-We can help with clinic brand site + whatsapp booking. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="Q34" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>https://uptodate.ae/</t>
         </is>
       </c>
     </row>
@@ -3916,8 +3982,10 @@
       <c r="O35" s="3" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Tallah 2, Ajman, UAE and noticed Delhi Private School Ajman's website looks outdated for today's market.
-We can help with school admissions website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
+I'm Vaibhav from DMC Creatives Studio (India). Parents comparing schools in Al Tallah 2 check the website on mobile before admissions calls — Delhi Private School Ajman's online presence could convert more enquiries.
+Happy to show how a cleaner admissions page + WhatsApp enquiry could look.
+We help with school admissions website + enquiry crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4017,8 +4085,10 @@
       <c r="O36" s="3" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in New Industrial Area, Doha, Qatar and noticed Etihad Steel Factory's website looks outdated for today's market.
-We can help with steel fabrication website + sales crm. If useful, I can share a quick redesign concept — no obligation.
+I'm Vaibhav from DMC Creatives Studio (India). I came across Etihad Steel Factory while reviewing industrial suppliers in New Industrial Area — steel structure factory contact is a sparse page; truck body/sales emails exist but the site does not sell capability..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with steel fabrication website + sales crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4114,8 +4184,10 @@
       <c r="O37" s="3" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Subhan Industrial Area, Kuwait and noticed Kuwait Saudi Pharmaceutical Industries Company (KSPICo)'s website looks outdated for today's market.
-We can help with pharma brand website rebuild. If useful, I can share a quick redesign concept — no obligation.
+I'm Vaibhav from DMC Creatives Studio (India). I came across Kuwait Saudi Pharmaceutical Industries Company (KSPICo) while reviewing industrial suppliers in Subhan Industrial Area — in-house 2020 site with repeated dummy copy on competence/reliability blocks — not a modern pharma brand site..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with pharma brand website rebuild. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4211,8 +4283,10 @@
       <c r="O38" s="3" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Ghala, Muscat / Sohar Free Zone, Oman and noticed Penicillin General Integrated Industrial Company (PenG)'s website looks outdated for today's market.
-We can help with industrial capability website + rfq. If useful, I can share a quick redesign concept — no obligation.
+I'm Vaibhav from DMC Creatives Studio (India). I came across Penicillin General Integrated Industrial Company (PenG) while reviewing industrial suppliers in Ghala — sohar Free Zone manufacturer contact is a thin page; API buyers expect a capability/compliance site..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with industrial capability website + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4308,8 +4382,10 @@
       <c r="O39" s="3" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Manakh, Sharjah, UAE and noticed Smart Engineering Coating Equipment Trading's website looks outdated for today's market.
-We can help with industrial trading website + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
+I'm Vaibhav from DMC Creatives Studio (India). I came across Smart Engineering Coating Equipment Trading while reviewing industrial suppliers in Al Manakh — content-protected industrial trader site; 15+ years in coating equipment but the web presence is a basic brochure..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with industrial trading website + enquiry crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4405,8 +4481,10 @@
       <c r="O40" s="3" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in 1st Industrial City, Dammam, Saudi Arabia and noticed The Saudi Transformers Company Ltd.'s website looks outdated for today's market.
-We can help with industrial brand site + rfq. If useful, I can share a quick redesign concept — no obligation.
+I'm Vaibhav from DMC Creatives Studio (India). I came across The Saudi Transformers Company Ltd. while reviewing industrial suppliers in 1st Industrial City — multi-city transformer manufacturer still using a basic branch-table contact page rather than a bid/RFQ portal..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with industrial brand site + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4502,8 +4580,10 @@
       <c r="O41" s="3" t="inlineStr">
         <is>
           <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Abraq 2, Umm Al Quwain, UAE and noticed Umm Al Quwain Rubber Industries Limited (URIL)'s website looks outdated for today's market.
-We can help with industrial rubber catalogue + enquiry crm. If useful, I can share a quick redesign concept — no obligation.
+I'm Vaibhav from DMC Creatives Studio (India). I came across Umm Al Quwain Rubber Industries Limited (URIL) while reviewing industrial suppliers in Al Abraq 2 — since-1992 rubber manufacturer; site claims 5+ years of experience in one block — inconsistent, brochure-only, no RFQ….
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with industrial rubber catalogue + enquiry crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
 Vaibhav Gurav
 DMC Creatives Studio
 hello@dmcstudio.in
@@ -4528,28 +4608,28 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId27"/>
@@ -4562,46 +4642,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId79"/>
@@ -4686,25 +4766,330 @@
     <row r="2" ht="100" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>AG Metal Industry LLC</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>info@agmetal.ae</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>+971 52 129 4509</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>AG Metal Industry LLC: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Al Jurf Industrial Area 2, Ajman, UAE, I came across AG Metal Industry LLC.
+I reviewed AG Metal Industry LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with fabrication brand site replacing godaddy builder. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across AG Metal Industry LLC while reviewing industrial suppliers in Al Jurf Industrial Area 2 — custom steel fabricator running a GoDaddy Website Builder page — looks like a placeholder vs ISO project work..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with fabrication brand site replacing godaddy builder. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="100" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Al Ramlah Garage</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>(use WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>+971 52 896 9596</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Al Ramlah Garage: test-drive leads are leaking online</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing automotive businesses in Al Qusais, Dubai / Al Khuzam, Ras Al Khaimah, UAE, I came across Al Ramlah Garage.
+I reviewed Al Ramlah Garage's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, test-drive and service bookings now start online — weak dealer sites lose leads to competitors.
+At DMC Creatives Studio we help Gulf businesses with garage website + whatsapp booking. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I checked Al Ramlah Garage's site — multi-branch garage site shows 0 happy customers / 0 experts — looks unfinished for Dubai and RAK service bookings..
+Most garage bookings in Dubai/RAK now start on Google or WhatsApp. A mobile site with service list + click-to-call helps you capture walk-ins.
+We help with garage website + whatsapp booking. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>No email</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="100" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sahara Medical Centre</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>info@saharamedicalcentre.ae</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>+971 50 882 1590</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sahara Medical Centre: patients shortlist clinics online first</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing healthcare businesses in Al Nahda, Sharjah, UAE, I came across Sahara Medical Centre.
+Sahara Medical Centre looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
+In this category, patients compare clinics online before they call — a clear website and booking path wins the enquiry.
+At DMC Creatives Studio we help Gulf businesses with new-clinic website + booking funnel. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I saw Sahara Medical Centre launching in Al Nahda — strong brand, but most enquiries still land on WhatsApp/Instagram instead of a owned website.
+A simple 5-page site (About, Services, Gallery, Contact + WhatsApp button) helps you look established when buyers Google you.
+We help with new-clinic website + booking funnel. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="100" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Emirates Industrial Filters Co.</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>info@eif.ae</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>+971 50 984 4298</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Emirates Industrial Filters Co.: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in New Industrial Area, Ajman, UAE, I came across Emirates Industrial Filters Co..
+I reviewed Emirates Industrial Filters Co.'s current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with b2b filtration catalogue + rfq. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Emirates Industrial Filters Co. while reviewing industrial suppliers in New Industrial Area — founded 2000 filtration manufacturer; site is a generic template with repeated CTAs, not a spec-sheet/RFQ catalogue..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with b2b filtration catalogue + rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Up To Date Medical Center</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>info@uptodate.ae</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>+971 50 680 5420</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Up To Date Medical Center: patients shortlist clinics online first</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing healthcare businesses in Al Dhiyafah, Dubai, UAE, I came across Up To Date Medical Center.
+I reviewed Up To Date Medical Center's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, patients compare clinics online before they call — a clear website and booking path wins the enquiry.
+At DMC Creatives Studio we help Gulf businesses with clinic brand site + whatsapp booking. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I was comparing clinics in Al Dhiyafah and noticed Up To Date Medical Center's website — elementor default-logo clinic site; name promises current care but the digital presence looks unfinished..
+Most patients shortlist 2–3 clinics on mobile before they call. A clean site with WhatsApp booking usually wins that first enquiry.
+We help with clinic brand site + whatsapp booking. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Adam Medical Centre</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>info@adammedicalcentre.com</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>+971 4 335 5011</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Adam Medical Centre: patients shortlist clinics online first</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Hi Saleel,
 While reviewing healthcare businesses in Dubai, UAE, I came across Adam Medical Centre.
@@ -4719,44 +5104,505 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="100" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Green Gold Lubricants</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>info@greengoldoils.com</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>+971 56 484 7356</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Green Gold Lubricants: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Al Sajja, Sharjah, UAE, I came across Green Gold Lubricants.
+I reviewed Green Gold Lubricants's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with brand + private-label catalogue website. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Green Gold Lubricants while reviewing industrial suppliers in Al Sajja — white-label lubricant maker with two WhatsApp numbers but a thin brand site vs OEM/catalogue buyers..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with brand + private-label catalogue website. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Al Mahboob Lubricants &amp; Oil Industries LLC</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>info@almahboobgroup.com</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>+971 50 746 8471</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Al Mahboob Lubricants &amp; Oil Industries LLC: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Industrial Area 11, Sharjah, UAE, I came across Al Mahboob Lubricants &amp; Oil Industries LLC.
+I reviewed Al Mahboob Lubricants &amp; Oil Industries LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with manufacturer catalogue site + rfq whatsapp crm. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Al Mahboob Lubricants &amp; Oil Industries LLC while reviewing industrial suppliers in Industrial Area 11 — 2002 lubricant manufacturer still on a basic slider brochure site; B2B buyers expect a product catalogue and RFQ path..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with manufacturer catalogue site + rfq whatsapp crm. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Al Najam Transport</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>alnajamllc@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>+971 52 953 3220</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Al Najam Transport's website still looks stuck in the past</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing services businesses in Ras Al Khaimah / Ajman, UAE, I came across Al Najam Transport.
+I reviewed Al Najam Transport's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, serious clients still Google you — a weak site quietly costs you deals.
+At DMC Creatives Studio we help Gulf businesses with transport company website + school-contract enquiry. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I reviewed Al Najam Transport in Ras Al Khaimah / Ajman — school-bus operator using Gmail and a thin service page instead of a parent-trust brand site for RAK/Ajman contracts..
+Local service buyers trust a proper website over Gmail/listing pages when they compare vendors.
+We help with transport company website + school-contract enquiry. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>NaasBay (HERBZE)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>(use WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>+971 58 103 9328</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>NaasBay: buyers search Google before they call</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing hotel / f&amp;b businesses in Dubai, UAE, I came across NaasBay (HERBZE).
+NaasBay (HERBZE) looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
+In this category, guests and corporates book the hotel that looks trustworthy and easy on mobile.
+At DMC Creatives Studio we help Gulf businesses with launch website + distributor landing page. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I saw NaasBay (HERBZE) launching in Dubai — strong brand, but most enquiries still land on WhatsApp/Instagram instead of a owned website.
+A simple 5-page site (About, Services, Gallery, Contact + WhatsApp button) helps you look established when buyers Google you.
+We help with launch website + distributor landing page. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>No email</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="100" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Green Gold Trading Company (Dubai)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>dubai@green-gold.co</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>+971 4 252 8284</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Green Gold Trading Company: buyers search Google before they call</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing trading businesses in Al Ras, Dubai, UAE, I came across Green Gold Trading Company (Dubai).
+Green Gold Trading Company (Dubai) looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
+In this category, importers and distributors lose RFQs when the catalogue site looks older than the stock.
+At DMC Creatives Studio we help Gulf businesses with uae branch website + enquiry crm. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>(no WhatsApp mobile)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>No WA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="100" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>SJS Enersol Engineering Works LLC</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>info@sjsenersol.ae</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>+971 56 761 6172</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>SJS Enersol Engineering Works LLC's website still looks stuck in the past</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing trading businesses in New Industrial Area, Umm Al Quwain, UAE, I came across SJS Enersol Engineering Works LLC.
+I reviewed SJS Enersol Engineering Works LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, importers and distributors lose RFQs when the catalogue site looks older than the stock.
+At DMC Creatives Studio we help Gulf businesses with one brand site + catalogue for fasteners and fabrication. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across SJS Enersol Engineering Works LLC while reviewing industrial suppliers in New Industrial Area — uAQ fasteners/pipes house with mixed domains (sjsenersol.ae vs sjsengg.ae) and a stockist site that does not match a….
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with one brand site + catalogue for fasteners and fabrication. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>CLICK WHATSAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="100" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>AL RIYADA Metal Industrial LLC</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>info@alriyadametals.com</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>+971 6 538 7221</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>AL RIYADA Metal Industrial LLC: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Emirates Industrial City, Al Sajja, Sharjah, UAE, I came across AL RIYADA Metal Industrial LLC.
+I reviewed AL RIYADA Metal Industrial LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with fabrication catalogue + rfq crm. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>(no WhatsApp mobile)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>No WA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="100" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>AL Muraqib Fiber Glass Industry L.L.C</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>info@almuraqib.ae</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>+971 6 569 1110</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>AL Muraqib Fiber Glass Industry L.L.C: RFQ buyers want a real catalogue site</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+While reviewing manufacturing businesses in Al Bataeh Industrial Area, Sharjah, UAE, I came across AL Muraqib Fiber Glass Industry L.L.C.
+I reviewed AL Muraqib Fiber Glass Industry L.L.C's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
+In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
+At DMC Creatives Studio we help Gulf businesses with industrial product site + quotation form. Happy to share a free one-page concept for your brand this week — no obligation.
+Regards,
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>(no WhatsApp mobile)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>CLICK TO EMAIL</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>No WA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="100" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Advanced Medical Center (AMC Muscat)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>info@amcmuscat.com</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>+968 9257 0007</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Advanced Medical Center: patients shortlist clinics online first</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing healthcare businesses in Qurum, Muscat, Oman, I came across Advanced Medical Center (AMC Muscat).
@@ -4771,391 +5617,53 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Qurum, Muscat, Oman and noticed Advanced Medical Center (AMC Muscat)'s website looks outdated for today's market.
-We can help with clinic website + whatsapp appointments. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I was comparing clinics in Qurum and noticed Advanced Medical Center (AMC Muscat)'s website — qurum polyclinic still on an old form/FAQ site; WhatsApp booking number exists but the digital experience is dated..
+Most patients shortlist 2–3 clinics on mobile before they call. A clean site with WhatsApp booking usually wins that first enquiry.
+We help with clinic website + whatsapp appointments. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="100" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>AG Metal Industry LLC</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>info@agmetal.ae</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>+971 52 129 4509</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>AG Metal Industry LLC: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Al Jurf Industrial Area 2, Ajman, UAE, I came across AG Metal Industry LLC.
-I reviewed AG Metal Industry LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with fabrication brand site replacing godaddy builder. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Jurf Industrial Area 2, Ajman, UAE and noticed AG Metal Industry LLC's website looks outdated for today's market.
-We can help with fabrication brand site replacing godaddy builder. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="100" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Al Mahboob Lubricants &amp; Oil Industries LLC</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>info@almahboobgroup.com</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>+971 50 746 8471</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Al Mahboob Lubricants &amp; Oil Industries LLC: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Industrial Area 11, Sharjah, UAE, I came across Al Mahboob Lubricants &amp; Oil Industries LLC.
-I reviewed Al Mahboob Lubricants &amp; Oil Industries LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with manufacturer catalogue site + rfq whatsapp crm. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Industrial Area 11, Sharjah, UAE and noticed Al Mahboob Lubricants &amp; Oil Industries LLC's website looks outdated for today's market.
-We can help with manufacturer catalogue site + rfq whatsapp crm. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>AL Muraqib Fiber Glass Industry L.L.C</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>info@almuraqib.ae</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>+971 6 569 1110</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>AL Muraqib Fiber Glass Industry L.L.C: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Al Bataeh Industrial Area, Sharjah, UAE, I came across AL Muraqib Fiber Glass Industry L.L.C.
-I reviewed AL Muraqib Fiber Glass Industry L.L.C's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with industrial product site + quotation form. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>(no WhatsApp mobile)</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>No WA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Al Najam Transport</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>alnajamllc@gmail.com</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>+971 52 953 3220</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Al Najam Transport's website still looks stuck in the past</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing services businesses in Ras Al Khaimah / Ajman, UAE, I came across Al Najam Transport.
-I reviewed Al Najam Transport's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, serious clients still Google you — a weak site quietly costs you deals.
-At DMC Creatives Studio we help Gulf businesses with transport company website + school-contract enquiry. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Ras Al Khaimah / Ajman, UAE and noticed Al Najam Transport's website looks outdated for today's market.
-We can help with transport company website + school-contract enquiry. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="100" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Al Ramlah Garage</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>(use WhatsApp)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>+971 52 896 9596</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Al Ramlah Garage: test-drive leads are leaking online</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing automotive businesses in Al Qusais, Dubai / Al Khuzam, Ras Al Khaimah, UAE, I came across Al Ramlah Garage.
-I reviewed Al Ramlah Garage's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, test-drive and service bookings now start online — weak dealer sites lose leads to competitors.
-At DMC Creatives Studio we help Gulf businesses with garage website + whatsapp booking. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Qusais, Dubai / Al Khuzam, Ras Al Khaimah, UAE and noticed Al Ramlah Garage's website looks outdated for today's market.
-We can help with garage website + whatsapp booking. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>No email</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>AL RIYADA Metal Industrial LLC</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>info@alriyadametals.com</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>+971 6 538 7221</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>AL RIYADA Metal Industrial LLC: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Emirates Industrial City, Al Sajja, Sharjah, UAE, I came across AL RIYADA Metal Industrial LLC.
-I reviewed AL RIYADA Metal Industrial LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with fabrication catalogue + rfq crm. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>(no WhatsApp mobile)</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>No WA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="100" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="17" ht="100" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Al-Noor Plastic Factory</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>info@npf.qa</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>+974 3399 9380</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Al-Noor Plastic Factory: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in New Industrial Area, Doha, Qatar, I came across Al-Noor Plastic Factory.
@@ -5170,106 +5678,49 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in New Industrial Area, Doha, Qatar and noticed Al-Noor Plastic Factory's website looks outdated for today's market.
-We can help with factory catalogue + whatsapp rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Al-Noor Plastic Factory while reviewing industrial suppliers in New Industrial Area — qatar industrial plastics plant; contact works but the brand site is a thin factory page vs GCC RFQ buyers..
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with factory catalogue + whatsapp rfq. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="100" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Emirates Industrial Filters Co.</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>info@eif.ae</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>+971 50 984 4298</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Emirates Industrial Filters Co.: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in New Industrial Area, Ajman, UAE, I came across Emirates Industrial Filters Co..
-I reviewed Emirates Industrial Filters Co.'s current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with b2b filtration catalogue + rfq. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in New Industrial Area, Ajman, UAE and noticed Emirates Industrial Filters Co.'s website looks outdated for today's market.
-We can help with b2b filtration catalogue + rfq. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="100" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="18" ht="100" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>epi AL-Ebda Plastic Industries</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>info@epi-qatar.com</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>epi AL-Ebda Plastic Industries: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in New Industrial Area, Doha, Qatar, I came across epi AL-Ebda Plastic Industries.
@@ -5284,103 +5735,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="100" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Green Gold Lubricants</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>info@greengoldoils.com</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>+971 56 484 7356</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Green Gold Lubricants: RFQ buyers want a real catalogue site</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing manufacturing businesses in Al Sajja, Sharjah, UAE, I came across Green Gold Lubricants.
-I reviewed Green Gold Lubricants's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, B2B buyers shortlist suppliers from Google and catalogue sites before they raise an RFQ.
-At DMC Creatives Studio we help Gulf businesses with brand + private-label catalogue website. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Sajja, Sharjah, UAE and noticed Green Gold Lubricants's website looks outdated for today's market.
-We can help with brand + private-label catalogue website. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="100" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="19" ht="100" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Green Gold Trading Co.</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>info@green-gold.co</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>920008925</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Green Gold Trading Co.'s website still looks stuck in the past</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing trading businesses in Al Aziziyah, Riyadh, Saudi Arabia, I came across Green Gold Trading Co..
@@ -5395,96 +5787,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="100" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Green Gold Trading Company (Dubai)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>dubai@green-gold.co</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>+971 4 252 8284</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Green Gold Trading Company: buyers search Google before they call</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing trading businesses in Al Ras, Dubai, UAE, I came across Green Gold Trading Company (Dubai).
-Green Gold Trading Company (Dubai) looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
-In this category, importers and distributors lose RFQs when the catalogue site looks older than the stock.
-At DMC Creatives Studio we help Gulf businesses with uae branch website + enquiry crm. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>(no WhatsApp mobile)</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>No WA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="100" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="20" ht="100" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>K-PAK (Kuwait Pack)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>kpak@kuwaitpack.com</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>+965 2472 1124</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>K-PAK: buyers search Google before they call</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in South Sabhan, Kuwait, I came across K-PAK (Kuwait Pack).
@@ -5499,44 +5839,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="100" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="21" ht="100" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Kuwait Polymer Company</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>info@kwpolymer.com</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>+965 2294 4544</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Kuwait Polymer Company: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Amgarah Industrial Area, Kuwait, I came across Kuwait Polymer Company.
@@ -5551,44 +5891,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="100" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="22" ht="100" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Manama Scientific Company</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>info@manamasc.com.bh</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>+973 1774 9010</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Manama Scientific Company's website still looks stuck in the past</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing trading businesses in Alqudaybiyah, Manama, Bahrain, I came across Manama Scientific Company.
@@ -5603,44 +5943,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="100" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="23" ht="100" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>MASABIK (Axles, Foundries &amp; Spare Parts Factory)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>sales@masabik.com</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>+966 13 812 1267</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>MASABIK: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Dammam Second Industrial City, Saudi Arabia, I came across MASABIK (Axles, Foundries &amp; Spare Parts Factory).
@@ -5655,44 +5995,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="100" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="24" ht="100" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Mekyal Muscat LLC</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>(use WhatsApp)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>+968 7904 9019</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Mekyal Muscat LLC: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Barka Industrial Estate, Oman, I came across Mekyal Muscat LLC.
@@ -5707,51 +6047,53 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Barka Industrial Estate, Oman and noticed Mekyal Muscat LLC's website looks outdated for today's market.
-We can help with instrumentation catalogue website. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I came across Mekyal Muscat LLC while reviewing industrial suppliers in Barka Industrial Estate — process-instrumentation manufacturer site has typos (Thermpcouples) and a 2023 template footer — not bid-ready for GCC….
+RFQ buyers in the UAE usually pick suppliers with a clear product catalogue and a WhatsApp quote button — not a thin brochure page.
+We help with instrumentation catalogue website. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>No email</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="100" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="25" ht="100" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>MPT Saudi Arabia</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>info@mpt.sa</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>+966 50 556 0191</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>MPT Saudi Arabia's website still looks stuck in the past</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing services businesses in Riyadh, Saudi Arabia, I came across MPT Saudi Arabia.
@@ -5766,51 +6108,53 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Riyadh, Saudi Arabia and noticed MPT Saudi Arabia's website looks outdated for today's market.
-We can help with agency website rebuild + arabic/english lead form. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I reviewed MPT Saudi Arabia in Riyadh — software/marketing firm site is broken (spaced testimonials, placeholder project names) — looks untrusted for Saudi….
+Local service buyers trust a proper website over Gmail/listing pages when they compare vendors.
+We help with agency website rebuild + arabic/english lead form. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="100" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="26" ht="100" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Muscat Express Hotel</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>info@muscatexpresshotel.com</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>+968 2255 3303</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Muscat Express Hotel: your website vs today's direct bookings</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing hotel / f&amp;b businesses in Al Ghubrah, Muscat, Oman, I came across Muscat Express Hotel.
@@ -5825,44 +6169,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="100" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="27" ht="100" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Muscat Hills Hotel</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>info@muscathillshotel.com</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>+968 9122 7323</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Muscat Hills Hotel: your website vs today's direct bookings</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing hotel / f&amp;b businesses in Ghala Heights, Bawsher, Muscat, Oman, I came across Muscat Hills Hotel.
@@ -5877,51 +6221,53 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Ghala Heights, Bawsher, Muscat, Oman and noticed Muscat Hills Hotel's website looks outdated for today's market.
-We can help with hotel website + direct-booking engine. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I was reviewing businesses in Ghala Heights and noticed Muscat Hills Hotel's website looks outdated for today's Gulf market.
+Buyers judge readiness from your website before they ever call.
+We help with hotel website + direct-booking engine. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="100" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="28" ht="100" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Muscat Steel Industries Co. LLC</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>info@muscatsteel.com</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>+968 2444 6938</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Muscat Steel Industries Co. LLC: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Rusayl, Muscat, Oman, I came across Muscat Steel Industries Co. LLC.
@@ -5936,103 +6282,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="100" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>NaasBay (HERBZE)</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>(use WhatsApp)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>+971 58 103 9328</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>NaasBay: buyers search Google before they call</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing hotel / f&amp;b businesses in Dubai, UAE, I came across NaasBay (HERBZE).
-NaasBay (HERBZE) looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
-In this category, guests and corporates book the hotel that looks trustworthy and easy on mobile.
-At DMC Creatives Studio we help Gulf businesses with launch website + distributor landing page. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing new businesses in Dubai, UAE and noticed NaasBay (HERBZE) still needs a conversion-ready website for the Gulf market.
-We can help with launch website + distributor landing page. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>No email</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="100" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="29" ht="100" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Qatar German Gasket Factory</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>sales@qger.com</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>+974 4411 4404</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Qatar German Gasket Factory is still on HTTP — that hurts trust</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in New Industrial Area, Doha, Qatar, I came across Qatar German Gasket Factory.
@@ -6047,44 +6334,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="100" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="30" ht="100" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Reef Yemen Company (Kuwait)</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>reefyemen.kwt@gmail.com</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>+965 2491 1837</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Reef Yemen Company's website still looks stuck in the past</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing trading businesses in Shuwaikh, Kuwait, I came across Reef Yemen Company (Kuwait).
@@ -6099,103 +6386,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="100" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Sahara Medical Centre</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>info@saharamedicalcentre.ae</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>+971 50 882 1590</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Sahara Medical Centre: patients shortlist clinics online first</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing healthcare businesses in Al Nahda, Sharjah, UAE, I came across Sahara Medical Centre.
-Sahara Medical Centre looks like a new / growing Gulf brand, but buyers still struggle to find a strong owned website they can trust.
-In this category, patients compare clinics online before they call — a clear website and booking path wins the enquiry.
-At DMC Creatives Studio we help Gulf businesses with new-clinic website + booking funnel. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing new businesses in Al Nahda, Sharjah, UAE and noticed Sahara Medical Centre still needs a conversion-ready website for the Gulf market.
-We can help with new-clinic website + booking funnel. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="100" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="31" ht="100" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Saudi Hadaid Factory</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>info@saudihadaid.com</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>+966 13 8309279</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Saudi Hadaid Factory: RFQ buyers want a real catalogue site</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Hi Fuad,
 While reviewing manufacturing businesses in 2nd Industrial City, Dammam, Saudi Arabia, I came across Saudi Hadaid Factory.
@@ -6210,44 +6438,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="100" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="32" ht="100" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Saudi Packing Materials Manufacturing Co. (S-PAK)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>spak@saudipack.com</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>+966 2 608 2088</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Saudi Packing Materials Manufacturing Co. is still on HTTP — that hurts trust</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in Jeddah Industrial City, Saudi Arabia, I came across Saudi Packing Materials Manufacturing Co. (S-PAK).
@@ -6262,103 +6490,44 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="100" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>SJS Enersol Engineering Works LLC</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>info@sjsenersol.ae</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>+971 56 761 6172</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>SJS Enersol Engineering Works LLC's website still looks stuck in the past</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing trading businesses in New Industrial Area, Umm Al Quwain, UAE, I came across SJS Enersol Engineering Works LLC.
-I reviewed SJS Enersol Engineering Works LLC's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, importers and distributors lose RFQs when the catalogue site looks older than the stock.
-At DMC Creatives Studio we help Gulf businesses with one brand site + catalogue for fasteners and fabrication. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in New Industrial Area, Umm Al Quwain, UAE and noticed SJS Enersol Engineering Works LLC's website looks outdated for today's market.
-We can help with one brand site + catalogue for fasteners and fabrication. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="100" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33" ht="100" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Tenhal Information Technology Company</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>info@tenhal.sa</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>+966 55 477 7441</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Tenhal Information Technology Company: a new Gulf brand still needs a real website</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing services businesses in King Faisal, Riyadh, Saudi Arabia, I came across Tenhal Information Technology Company.
@@ -6373,51 +6542,53 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing new businesses in King Faisal, Riyadh, Saudi Arabia and noticed Tenhal Information Technology Company still needs a conversion-ready website for the Gulf market.
-We can help with new-company website + lead capture. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Hello,
+I'm Vaibhav from DMC Creatives Studio (India). I saw Tenhal Information Technology Company launching in King Faisal — strong brand, but most enquiries still land on WhatsApp/Instagram instead of a owned website.
+A simple 5-page site (About, Services, Gallery, Contact + WhatsApp button) helps you look established when buyers Google you.
+We help with new-company website + lead capture. Packages from ~AED 2,500 for SMEs.
+I can share a free one-page mockup this week — no obligation.
+Vaibhav Gurav
+DMC Creatives Studio
+hello@dmcstudio.in
+www.dmcstudio.in
++91 83693 61785</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>CLICK WHATSAPP</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="100" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34" ht="100" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>U-PAK FZC</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>upak@upakfzc.com</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>+971 7 244 7950</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>U-PAK FZC is still on HTTP — that hurts trust</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Hello,
 While reviewing manufacturing businesses in RAK Free Trade Zone, Ras Al Khaimah, UAE, I came across U-PAK FZC.
@@ -6432,129 +6603,70 @@
 +91 83693 61785</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>(no WhatsApp mobile)</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>CLICK TO EMAIL</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>No WA</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="100" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Up To Date Medical Center</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>info@uptodate.ae</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>+971 50 680 5420</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Up To Date Medical Center: patients shortlist clinics online first</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-While reviewing healthcare businesses in Al Dhiyafah, Dubai, UAE, I came across Up To Date Medical Center.
-I reviewed Up To Date Medical Center's current digital presence — it works, but it no longer feels current or conversion-ready for today's GCC market.
-In this category, patients compare clinics online before they call — a clear website and booking path wins the enquiry.
-At DMC Creatives Studio we help Gulf businesses with clinic brand site + whatsapp booking. Happy to share a free one-page concept for your brand this week — no obligation.
-Regards,
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Hello,
-I'm Vaibhav from DMC Creatives Studio. I was reviewing businesses in Al Dhiyafah, Dubai, UAE and noticed Up To Date Medical Center's website looks outdated for today's market.
-We can help with clinic brand site + whatsapp booking. If useful, I can share a quick redesign concept — no obligation.
-Vaibhav Gurav
-DMC Creatives Studio
-hello@dmcstudio.in
-www.dmcstudio.in
-+91 83693 61785</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>CLICK TO EMAIL</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>CLICK WHATSAPP</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
